--- a/test-data/2.半成品期末库存.xlsx
+++ b/test-data/2.半成品期末库存.xlsx
@@ -50,7 +50,7 @@
     <t>207200037D</t>
   </si>
   <si>
-    <t>20260531-1</t>
+    <t>20260531-2</t>
   </si>
   <si>
     <t>206200084D</t>
